--- a/artfynd/A 37388-2025 artfynd.xlsx
+++ b/artfynd/A 37388-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>79846496</v>
       </c>
       <c r="B2" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>391498.5386062338</v>
+        <v>391499</v>
       </c>
       <c r="R2" t="n">
-        <v>6719325.989391546</v>
+        <v>6719326</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -758,19 +753,9 @@
           <t>2019-09-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,12 +785,7 @@
         <v>79888245</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>391257.714764395</v>
+        <v>391258</v>
       </c>
       <c r="R3" t="n">
-        <v>6719209.386921499</v>
+        <v>6719209</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +853,9 @@
           <t>2019-09-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79888248</v>
+        <v>79888254</v>
       </c>
       <c r="B4" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,25 +894,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -956,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>391278.6413546375</v>
+        <v>391323</v>
       </c>
       <c r="R4" t="n">
-        <v>6719217.602823082</v>
+        <v>6719242</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,19 +962,9 @@
           <t>2019-09-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,15 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79888254</v>
+        <v>79888248</v>
       </c>
       <c r="B5" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,33 +1003,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1080,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>391323.2056877457</v>
+        <v>391279</v>
       </c>
       <c r="R5" t="n">
-        <v>6719242.30930622</v>
+        <v>6719218</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,19 +1063,9 @@
           <t>2019-09-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,6 +1090,311 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>79846385</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Möresberget , Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>391386</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6719282</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>79846243</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Möresberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>391365</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6719269</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>79846511</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Möresberget , Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>391499</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6719326</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37388-2025 artfynd.xlsx
+++ b/artfynd/A 37388-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79846496</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79888245</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79888254</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79888248</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79846385</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79846243</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,8 +1430,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79846511</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>